--- a/CP200_db.xlsx
+++ b/CP200_db.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet2" sheetId="12" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$B$358</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$B$361</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="459">
   <si>
     <t>Gene</t>
   </si>
@@ -1392,6 +1392,21 @@
   </si>
   <si>
     <t>NM_002439.5:exon1:c.182_183insGGCGCCCGC:p.(A61_P63dup):p.(Ala61_Pro63dup)</t>
+  </si>
+  <si>
+    <t>NM_002890.3:intron13:c.1777-18_1777-15dup:p.?:p.?</t>
+  </si>
+  <si>
+    <t>RAD50</t>
+  </si>
+  <si>
+    <t>NM_005732.4:exon13:c.2165dup:p.(E723Gfs*5):p.(Glu723GlyfsTer5)</t>
+  </si>
+  <si>
+    <t>NM_002392.6:intron4:c.309-13_309-12dup:p.?:p.?</t>
+  </si>
+  <si>
+    <t>NM_170606.3:intron37:c.7443-6_7443-5insTTTTTTTTTTTA:p.?:p.?</t>
   </si>
 </sst>
 </file>
@@ -2017,28 +2032,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2401,7 +2407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.5454545454545" style="1" customWidth="1"/>
@@ -2410,2878 +2416,2922 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="3" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" spans="1:2">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="67" s="1" customFormat="1" spans="1:2">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="3" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="68" s="1" customFormat="1" spans="1:2">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="69" s="1" customFormat="1" spans="1:2">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="70" s="1" customFormat="1" spans="1:2">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="3" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="71" s="1" customFormat="1" spans="1:2">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="3" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="72" s="1" customFormat="1" spans="1:2">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="73" s="1" customFormat="1" spans="1:2">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" s="1" customFormat="1" spans="1:2">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="75" s="1" customFormat="1" spans="1:2">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="76" s="1" customFormat="1" spans="1:2">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:2">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:2">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:2">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" spans="1:2">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="81" s="1" customFormat="1" spans="1:2">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" spans="1:2">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" spans="1:2">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="84" s="1" customFormat="1" spans="1:2">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="85" s="1" customFormat="1" spans="1:2">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="86" s="1" customFormat="1" spans="1:2">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="3" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="87" s="1" customFormat="1" spans="1:2">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="88" s="1" customFormat="1" spans="1:2">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="89" s="1" customFormat="1" spans="1:2">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="90" s="1" customFormat="1" spans="1:2">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="91" s="1" customFormat="1" spans="1:2">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" spans="1:2">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="3" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="1:2">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="3" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="1:2">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="3" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="1:2">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="1:2">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="1:2">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="1:2">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="1:2">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="1:2">
-      <c r="A100" s="7" t="s">
+      <c r="A100" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="5" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="1:2">
-      <c r="A101" s="7" t="s">
+      <c r="A101" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="5" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="1:2">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="3" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="1:2">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="1:2">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="1:2">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="1:2">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="1:2">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="1:2">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="1:2">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="110" s="1" customFormat="1" spans="1:2">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="3" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="111" s="1" customFormat="1" spans="1:2">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="1:2">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="113" s="1" customFormat="1" spans="1:2">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="114" s="1" customFormat="1" spans="1:2">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="3" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="115" s="1" customFormat="1" spans="1:2">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="3" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="116" s="1" customFormat="1" spans="1:2">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="3" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="117" s="1" customFormat="1" spans="1:2">
-      <c r="A117" s="3" t="s">
+      <c r="A117" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="118" s="1" customFormat="1" spans="1:2">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="119" s="1" customFormat="1" spans="1:2">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="3" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="120" s="1" customFormat="1" spans="1:2">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" spans="1:2">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="122" s="1" customFormat="1" spans="1:2">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="123" s="1" customFormat="1" spans="1:2">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="124" s="1" customFormat="1" spans="1:2">
-      <c r="A124" s="5" t="s">
+      <c r="A124" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="125" s="1" customFormat="1" spans="1:2">
-      <c r="A125" s="5" t="s">
+      <c r="A125" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="126" s="1" customFormat="1" spans="1:2">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="127" s="1" customFormat="1" spans="1:2">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="128" s="1" customFormat="1" spans="1:2">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="129" s="1" customFormat="1" spans="1:2">
-      <c r="A129" s="5" t="s">
+      <c r="A129" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="130" s="1" customFormat="1" spans="1:2">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B130" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="131" s="1" customFormat="1" spans="1:2">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B131" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="132" s="1" customFormat="1" spans="1:2">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="133" s="1" customFormat="1" spans="1:2">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B133" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="134" s="1" customFormat="1" spans="1:2">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="3" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="135" s="1" customFormat="1" spans="1:2">
-      <c r="A135" s="3" t="s">
+      <c r="A135" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="136" s="1" customFormat="1" spans="1:2">
-      <c r="A136" s="3" t="s">
+      <c r="A136" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="137" s="1" customFormat="1" spans="1:2">
-      <c r="A137" s="3" t="s">
+      <c r="A137" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="138" s="1" customFormat="1" spans="1:2">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="3" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="139" s="1" customFormat="1" spans="1:2">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="140" s="1" customFormat="1" spans="1:2">
-      <c r="A140" s="3" t="s">
+      <c r="A140" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="141" s="1" customFormat="1" spans="1:2">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="3" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="142" s="1" customFormat="1" spans="1:2">
-      <c r="A142" s="3" t="s">
+      <c r="A142" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="143" s="1" customFormat="1" spans="1:2">
-      <c r="A143" s="3" t="s">
+      <c r="A143" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="144" s="1" customFormat="1" spans="1:2">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="3" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="145" s="1" customFormat="1" spans="1:2">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="3" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="146" s="1" customFormat="1" spans="1:2">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="3" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="147" s="1" customFormat="1" spans="1:2">
-      <c r="A147" s="3" t="s">
+      <c r="A147" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="148" s="1" customFormat="1" spans="1:2">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="1" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="149" s="1" customFormat="1" spans="1:2">
-      <c r="A149" s="5" t="s">
+      <c r="A149" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="150" s="1" customFormat="1" spans="1:2">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="3" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="151" s="1" customFormat="1" spans="1:2">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="3" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="152" s="1" customFormat="1" spans="1:2">
-      <c r="A152" s="3" t="s">
+      <c r="A152" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="1" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="153" s="1" customFormat="1" spans="1:2">
-      <c r="A153" s="3" t="s">
+      <c r="A153" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="154" s="1" customFormat="1" spans="1:2">
-      <c r="A154" s="3" t="s">
+      <c r="A154" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="155" s="1" customFormat="1" spans="1:2">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B155" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="156" s="1" customFormat="1" spans="1:2">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="157" s="1" customFormat="1" spans="1:2">
-      <c r="A157" s="3" t="s">
+      <c r="A157" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="158" s="1" customFormat="1" spans="1:2">
-      <c r="A158" s="3" t="s">
+      <c r="A158" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="159" s="1" customFormat="1" spans="1:2">
-      <c r="A159" s="3" t="s">
+      <c r="A159" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="160" s="1" customFormat="1" spans="1:2">
-      <c r="A160" s="3" t="s">
+      <c r="A160" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="161" s="1" customFormat="1" spans="1:2">
-      <c r="A161" s="3" t="s">
+      <c r="A161" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="162" s="1" customFormat="1" spans="1:2">
-      <c r="A162" s="5" t="s">
+      <c r="A162" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="163" s="1" customFormat="1" spans="1:2">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B163" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="164" s="1" customFormat="1" spans="1:2">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="165" s="1" customFormat="1" spans="1:2">
-      <c r="A165" s="5" t="s">
+      <c r="A165" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="166" s="1" customFormat="1" spans="1:2">
-      <c r="A166" s="5" t="s">
+      <c r="A166" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="167" s="1" customFormat="1" spans="1:2">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="168" s="1" customFormat="1" spans="1:2">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="3" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="169" s="1" customFormat="1" spans="1:2">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="3" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="170" s="1" customFormat="1" spans="1:2">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="171" s="1" customFormat="1" spans="1:2">
-      <c r="A171" s="4" t="s">
+      <c r="A171" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="3" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="172" s="1" customFormat="1" spans="1:2">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="3" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="173" s="1" customFormat="1" spans="1:2">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="3" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="174" s="1" customFormat="1" spans="1:2">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="3" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="175" s="1" customFormat="1" spans="1:2">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="3" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="176" s="1" customFormat="1" spans="1:2">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="3" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="177" s="1" customFormat="1" spans="1:2">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="3" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="178" s="1" customFormat="1" spans="1:2">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="3" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="179" s="1" customFormat="1" spans="1:2">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="3" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="180" s="1" customFormat="1" spans="1:2">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="3" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="181" s="1" customFormat="1" spans="1:2">
-      <c r="A181" s="4" t="s">
+      <c r="A181" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B181" s="4" t="s">
+      <c r="B181" s="3" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="182" s="1" customFormat="1" spans="1:2">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="3" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="183" s="1" customFormat="1" spans="1:2">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="184" s="1" customFormat="1" spans="1:2">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="3" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="185" s="1" customFormat="1" spans="1:2">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="3" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="186" s="1" customFormat="1" spans="1:2">
-      <c r="A186" s="3" t="s">
+      <c r="A186" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="187" s="1" customFormat="1" spans="1:2">
-      <c r="A187" s="3" t="s">
+      <c r="A187" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="1" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="188" s="1" customFormat="1" spans="1:2">
-      <c r="A188" s="3" t="s">
+      <c r="A188" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="1" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="189" s="1" customFormat="1" spans="1:2">
-      <c r="A189" s="3" t="s">
+      <c r="A189" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="190" s="1" customFormat="1" spans="1:2">
-      <c r="A190" s="3" t="s">
+      <c r="A190" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" spans="1:2">
-      <c r="A191" s="3" t="s">
+      <c r="A191" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="192" s="1" customFormat="1" spans="1:2">
-      <c r="A192" s="3" t="s">
+      <c r="A192" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="193" s="1" customFormat="1" spans="1:2">
-      <c r="A193" s="3" t="s">
+      <c r="A193" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="194" s="1" customFormat="1" spans="1:2">
-      <c r="A194" s="3" t="s">
+      <c r="A194" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="1" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="195" s="1" customFormat="1" spans="1:2">
-      <c r="A195" s="3" t="s">
+      <c r="A195" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="1" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="196" s="1" customFormat="1" spans="1:2">
-      <c r="A196" s="5" t="s">
+      <c r="A196" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B196" s="1" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="197" s="1" customFormat="1" spans="1:2">
-      <c r="A197" s="5" t="s">
+      <c r="A197" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="B197" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="198" s="1" customFormat="1" spans="1:2">
-      <c r="A198" s="5" t="s">
+      <c r="A198" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B198" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" spans="1:2">
-      <c r="A199" s="3" t="s">
+      <c r="A199" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="200" s="1" customFormat="1" spans="1:2">
-      <c r="A200" s="3" t="s">
+      <c r="A200" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="201" s="1" customFormat="1" spans="1:2">
-      <c r="A201" s="3" t="s">
+      <c r="A201" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="1" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="202" s="1" customFormat="1" spans="1:2">
-      <c r="A202" s="3" t="s">
+      <c r="A202" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="203" s="1" customFormat="1" spans="1:2">
-      <c r="A203" s="3" t="s">
+      <c r="A203" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="204" s="1" customFormat="1" spans="1:2">
-      <c r="A204" s="3" t="s">
+      <c r="A204" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="1" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="1" spans="1:2">
-      <c r="A205" s="3" t="s">
+      <c r="A205" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="206" s="1" customFormat="1" spans="1:2">
-      <c r="A206" s="3" t="s">
+      <c r="A206" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="207" s="1" customFormat="1" spans="1:2">
-      <c r="A207" s="3" t="s">
+      <c r="A207" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="208" s="1" customFormat="1" spans="1:2">
-      <c r="A208" s="3" t="s">
+      <c r="A208" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="1" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="209" s="1" customFormat="1" spans="1:2">
-      <c r="A209" s="3" t="s">
+      <c r="A209" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="210" s="1" customFormat="1" spans="1:2">
-      <c r="A210" s="3" t="s">
+      <c r="A210" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="211" s="1" customFormat="1" spans="1:2">
-      <c r="A211" s="3" t="s">
+      <c r="A211" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="212" s="1" customFormat="1" spans="1:2">
-      <c r="A212" s="3" t="s">
+      <c r="A212" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="213" s="1" customFormat="1" spans="1:2">
-      <c r="A213" s="3" t="s">
+      <c r="A213" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="1" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="214" s="1" customFormat="1" spans="1:2">
-      <c r="A214" s="3" t="s">
+      <c r="A214" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="1" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="215" s="1" customFormat="1" spans="1:2">
-      <c r="A215" s="3" t="s">
+      <c r="A215" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="216" s="1" customFormat="1" spans="1:2">
-      <c r="A216" s="3" t="s">
+      <c r="A216" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="217" s="1" customFormat="1" spans="1:2">
-      <c r="A217" s="3" t="s">
+      <c r="A217" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="218" s="1" customFormat="1" spans="1:2">
-      <c r="A218" s="3" t="s">
+      <c r="A218" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" spans="1:2">
-      <c r="A219" s="5" t="s">
+      <c r="A219" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="B219" s="1" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="220" s="1" customFormat="1" spans="1:2">
-      <c r="A220" s="3" t="s">
+      <c r="A220" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="221" s="1" customFormat="1" spans="1:2">
-      <c r="A221" s="5" t="s">
+      <c r="A221" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="B221" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" spans="1:2">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B222" s="4" t="s">
+      <c r="B222" s="3" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="223" s="1" customFormat="1" spans="1:2">
-      <c r="A223" s="4" t="s">
+      <c r="A223" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="3" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="224" s="1" customFormat="1" spans="1:2">
-      <c r="A224" s="3" t="s">
+      <c r="A224" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="1" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="225" s="1" customFormat="1" spans="1:2">
-      <c r="A225" s="3" t="s">
+      <c r="A225" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="226" s="1" customFormat="1" spans="1:2">
-      <c r="A226" s="5" t="s">
+      <c r="A226" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B226" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="227" s="1" customFormat="1" spans="1:2">
-      <c r="A227" s="4" t="s">
+      <c r="A227" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B227" s="4" t="s">
+      <c r="B227" s="3" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="228" s="1" customFormat="1" spans="1:2">
-      <c r="A228" s="4" t="s">
+      <c r="A228" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="3" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" spans="1:2">
-      <c r="A229" s="3" t="s">
+      <c r="A229" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="230" s="1" customFormat="1" spans="1:2">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="1" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="231" s="1" customFormat="1" spans="1:2">
-      <c r="A231" s="3" t="s">
+      <c r="A231" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="232" s="1" customFormat="1" spans="1:2">
-      <c r="A232" s="3" t="s">
+      <c r="A232" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="1" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="233" s="1" customFormat="1" spans="1:2">
-      <c r="A233" s="4" t="s">
+      <c r="A233" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B233" s="4" t="s">
+      <c r="B233" s="3" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="234" s="1" customFormat="1" spans="1:2">
-      <c r="A234" s="4" t="s">
+      <c r="A234" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="3" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="235" s="1" customFormat="1" spans="1:2">
-      <c r="A235" s="4" t="s">
+      <c r="A235" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B235" s="4" t="s">
+      <c r="B235" s="3" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="236" s="1" customFormat="1" spans="1:2">
-      <c r="A236" s="4" t="s">
+      <c r="A236" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B236" s="3" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="237" s="1" customFormat="1" spans="1:2">
-      <c r="A237" s="4" t="s">
+      <c r="A237" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B237" s="4" t="s">
+      <c r="B237" s="3" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="238" s="1" customFormat="1" spans="1:2">
-      <c r="A238" s="5" t="s">
+      <c r="A238" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B238" s="5" t="s">
+      <c r="B238" s="1" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="239" s="1" customFormat="1" spans="1:2">
-      <c r="A239" s="3" t="s">
+      <c r="A239" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B239" s="3" t="s">
+      <c r="B239" s="1" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="240" s="1" customFormat="1" spans="1:2">
-      <c r="A240" s="3" t="s">
+      <c r="A240" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B240" s="3" t="s">
+      <c r="B240" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="241" s="1" customFormat="1" spans="1:2">
-      <c r="A241" s="4" t="s">
+      <c r="A241" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B241" s="4" t="s">
+      <c r="B241" s="3" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="242" s="1" customFormat="1" spans="1:2">
-      <c r="A242" s="5" t="s">
+      <c r="A242" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B242" s="5" t="s">
+      <c r="B242" s="1" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="243" s="1" customFormat="1" spans="1:2">
-      <c r="A243" s="3" t="s">
+      <c r="A243" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B243" s="3" t="s">
+      <c r="B243" s="1" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="244" s="1" customFormat="1" spans="1:2">
-      <c r="A244" s="3" t="s">
+      <c r="A244" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B244" s="3" t="s">
+      <c r="B244" s="1" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="245" s="1" customFormat="1" spans="1:2">
-      <c r="A245" s="3" t="s">
+      <c r="A245" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B245" s="3" t="s">
+      <c r="B245" s="1" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="246" s="1" customFormat="1" spans="1:2">
-      <c r="A246" s="5" t="s">
+      <c r="A246" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="B246" s="1" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="247" s="1" customFormat="1" spans="1:2">
-      <c r="A247" s="3" t="s">
+      <c r="A247" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B247" s="3" t="s">
+      <c r="B247" s="1" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="248" s="1" customFormat="1" spans="1:2">
-      <c r="A248" s="3" t="s">
+      <c r="A248" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B248" s="1" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="249" s="1" customFormat="1" spans="1:2">
-      <c r="A249" s="5" t="s">
+      <c r="A249" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B249" s="5" t="s">
+      <c r="B249" s="1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="250" s="1" customFormat="1" spans="1:2">
-      <c r="A250" s="4" t="s">
+      <c r="A250" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="3" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="251" s="1" customFormat="1" spans="1:2">
-      <c r="A251" s="4" t="s">
+      <c r="A251" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B251" s="3" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="252" s="1" customFormat="1" spans="1:2">
-      <c r="A252" s="3" t="s">
+      <c r="A252" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B252" s="3" t="s">
+      <c r="B252" s="1" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="1" spans="1:2">
-      <c r="A253" s="3" t="s">
+      <c r="A253" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B253" s="3" t="s">
+      <c r="B253" s="1" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="254" s="1" customFormat="1" spans="1:2">
-      <c r="A254" s="3" t="s">
+      <c r="A254" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B254" s="3" t="s">
+      <c r="B254" s="1" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="255" s="1" customFormat="1" spans="1:2">
-      <c r="A255" s="3" t="s">
+      <c r="A255" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B255" s="3" t="s">
+      <c r="B255" s="1" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="256" s="1" customFormat="1" spans="1:2">
-      <c r="A256" s="4" t="s">
+      <c r="A256" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="3" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="257" s="1" customFormat="1" spans="1:2">
-      <c r="A257" s="4" t="s">
+      <c r="A257" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B257" s="4" t="s">
+      <c r="B257" s="3" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="258" s="1" customFormat="1" spans="1:2">
-      <c r="A258" s="3" t="s">
+      <c r="A258" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B258" s="3" t="s">
+      <c r="B258" s="1" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="259" s="1" customFormat="1" spans="1:2">
-      <c r="A259" s="3" t="s">
+      <c r="A259" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B259" s="3" t="s">
+      <c r="B259" s="1" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="260" s="1" customFormat="1" spans="1:2">
-      <c r="A260" s="3" t="s">
+      <c r="A260" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B260" s="3" t="s">
+      <c r="B260" s="1" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="261" s="1" customFormat="1" spans="1:2">
-      <c r="A261" s="3" t="s">
+      <c r="A261" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B261" s="3" t="s">
+      <c r="B261" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="262" s="1" customFormat="1" spans="1:2">
-      <c r="A262" s="3" t="s">
+      <c r="A262" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B262" s="3" t="s">
+      <c r="B262" s="1" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="263" s="1" customFormat="1" spans="1:2">
-      <c r="A263" s="3" t="s">
+      <c r="A263" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B263" s="1" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="264" s="1" customFormat="1" spans="1:2">
-      <c r="A264" s="5" t="s">
+      <c r="A264" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B264" s="5" t="s">
+      <c r="B264" s="1" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="265" s="1" customFormat="1" spans="1:2">
-      <c r="A265" s="3" t="s">
+      <c r="A265" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B265" s="3" t="s">
+      <c r="B265" s="1" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="266" s="1" customFormat="1" spans="1:2">
-      <c r="A266" s="3" t="s">
+      <c r="A266" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B266" s="3" t="s">
+      <c r="B266" s="1" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="267" s="1" customFormat="1" spans="1:2">
-      <c r="A267" s="3" t="s">
+      <c r="A267" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B267" s="3" t="s">
+      <c r="B267" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="268" s="1" customFormat="1" spans="1:2">
-      <c r="A268" s="5" t="s">
+      <c r="A268" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B268" s="5" t="s">
+      <c r="B268" s="1" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="269" s="1" customFormat="1" spans="1:2">
-      <c r="A269" s="5" t="s">
+      <c r="A269" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B269" s="5" t="s">
+      <c r="B269" s="1" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="270" s="1" customFormat="1" spans="1:2">
-      <c r="A270" s="5" t="s">
+      <c r="A270" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="B270" s="1" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="271" s="1" customFormat="1" spans="1:2">
-      <c r="A271" s="5" t="s">
+      <c r="A271" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B271" s="5" t="s">
+      <c r="B271" s="1" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="272" s="1" customFormat="1" spans="1:2">
-      <c r="A272" s="4" t="s">
+      <c r="A272" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B272" s="3" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="273" s="1" customFormat="1" spans="1:2">
-      <c r="A273" s="4" t="s">
+      <c r="A273" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="3" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="274" s="1" customFormat="1" spans="1:2">
-      <c r="A274" s="4" t="s">
+      <c r="A274" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B274" s="4" t="s">
+      <c r="B274" s="3" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="275" s="1" customFormat="1" spans="1:2">
-      <c r="A275" s="4" t="s">
+      <c r="A275" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="3" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="276" s="1" customFormat="1" spans="1:2">
-      <c r="A276" s="4" t="s">
+      <c r="A276" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B276" s="4" t="s">
+      <c r="B276" s="3" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="277" s="1" customFormat="1" spans="1:2">
-      <c r="A277" s="4" t="s">
+      <c r="A277" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="3" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="278" s="1" customFormat="1" spans="1:2">
-      <c r="A278" s="4" t="s">
+      <c r="A278" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B278" s="4" t="s">
+      <c r="B278" s="3" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="279" s="1" customFormat="1" spans="1:2">
-      <c r="A279" s="4" t="s">
+      <c r="A279" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="3" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="280" s="1" customFormat="1" spans="1:2">
-      <c r="A280" s="3" t="s">
+      <c r="A280" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B280" s="3" t="s">
+      <c r="B280" s="1" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="281" s="1" customFormat="1" spans="1:2">
-      <c r="A281" s="4" t="s">
+      <c r="A281" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="3" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="282" s="1" customFormat="1" spans="1:2">
-      <c r="A282" s="3" t="s">
+      <c r="A282" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B282" s="3" t="s">
+      <c r="B282" s="1" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="283" s="1" customFormat="1" spans="1:2">
-      <c r="A283" s="3" t="s">
+      <c r="A283" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B283" s="3" t="s">
+      <c r="B283" s="1" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="284" s="1" customFormat="1" spans="1:2">
-      <c r="A284" s="5" t="s">
+      <c r="A284" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B284" s="5" t="s">
+      <c r="B284" s="1" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="285" s="1" customFormat="1" spans="1:2">
-      <c r="A285" s="5" t="s">
+      <c r="A285" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B285" s="5" t="s">
+      <c r="B285" s="1" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="286" s="1" customFormat="1" spans="1:2">
-      <c r="A286" s="3" t="s">
+      <c r="A286" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B286" s="3" t="s">
+      <c r="B286" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="287" s="1" customFormat="1" spans="1:2">
-      <c r="A287" s="4" t="s">
+      <c r="A287" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="3" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="288" s="1" customFormat="1" spans="1:2">
-      <c r="A288" s="4" t="s">
+      <c r="A288" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B288" s="4" t="s">
+      <c r="B288" s="3" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="289" s="1" customFormat="1" spans="1:2">
-      <c r="A289" s="4" t="s">
+      <c r="A289" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B289" s="3" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="290" s="1" customFormat="1" spans="1:2">
-      <c r="A290" s="4" t="s">
+      <c r="A290" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B290" s="4" t="s">
+      <c r="B290" s="3" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="291" s="1" customFormat="1" spans="1:2">
-      <c r="A291" s="4" t="s">
+      <c r="A291" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B291" s="4" t="s">
+      <c r="B291" s="3" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="292" s="1" customFormat="1" spans="1:2">
-      <c r="A292" s="4" t="s">
+      <c r="A292" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="B292" s="3" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="293" s="1" customFormat="1" spans="1:2">
-      <c r="A293" s="4" t="s">
+      <c r="A293" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B293" s="3" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="294" s="1" customFormat="1" spans="1:2">
-      <c r="A294" s="4" t="s">
+      <c r="A294" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B294" s="3" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="295" s="1" customFormat="1" spans="1:2">
-      <c r="A295" s="4" t="s">
+      <c r="A295" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B295" s="4" t="s">
+      <c r="B295" s="3" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="296" s="1" customFormat="1" spans="1:2">
-      <c r="A296" s="4" t="s">
+      <c r="A296" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B296" s="3" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="297" s="1" customFormat="1" spans="1:2">
-      <c r="A297" s="4" t="s">
+      <c r="A297" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B297" s="4" t="s">
+      <c r="B297" s="3" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="298" s="1" customFormat="1" spans="1:2">
-      <c r="A298" s="4" t="s">
+      <c r="A298" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B298" s="4" t="s">
+      <c r="B298" s="3" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="299" s="1" customFormat="1" spans="1:2">
-      <c r="A299" s="4" t="s">
+      <c r="A299" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B299" s="4" t="s">
+      <c r="B299" s="3" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="300" s="1" customFormat="1" spans="1:2">
-      <c r="A300" s="4" t="s">
+      <c r="A300" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="3" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="301" s="1" customFormat="1" spans="1:2">
-      <c r="A301" s="4" t="s">
+      <c r="A301" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="B301" s="4" t="s">
+      <c r="B301" s="3" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="302" s="1" customFormat="1" spans="1:2">
-      <c r="A302" s="3" t="s">
+      <c r="A302" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B302" s="3" t="s">
+      <c r="B302" s="1" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="303" s="1" customFormat="1" spans="1:2">
-      <c r="A303" s="3" t="s">
+      <c r="A303" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B303" s="3" t="s">
+      <c r="B303" s="1" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="304" s="1" customFormat="1" spans="1:2">
-      <c r="A304" s="3" t="s">
+      <c r="A304" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B304" s="3" t="s">
+      <c r="B304" s="1" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="1" spans="1:2">
-      <c r="A305" s="3" t="s">
+      <c r="A305" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B305" s="3" t="s">
+      <c r="B305" s="1" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="306" s="1" customFormat="1" spans="1:2">
-      <c r="A306" s="3" t="s">
+      <c r="A306" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B306" s="3" t="s">
+      <c r="B306" s="1" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="307" s="1" customFormat="1" spans="1:2">
-      <c r="A307" s="3" t="s">
+      <c r="A307" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B307" s="3" t="s">
+      <c r="B307" s="1" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="308" s="1" customFormat="1" spans="1:2">
-      <c r="A308" s="3" t="s">
+      <c r="A308" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B308" s="3" t="s">
+      <c r="B308" s="1" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="309" s="1" customFormat="1" spans="1:2">
-      <c r="A309" s="4" t="s">
+      <c r="A309" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B309" s="4" t="s">
+      <c r="B309" s="3" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="310" s="1" customFormat="1" spans="1:2">
-      <c r="A310" s="4" t="s">
+      <c r="A310" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B310" s="4" t="s">
+      <c r="B310" s="3" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="311" s="1" customFormat="1" spans="1:2">
-      <c r="A311" s="3" t="s">
+      <c r="A311" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B311" s="3" t="s">
+      <c r="B311" s="1" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="312" s="1" customFormat="1" spans="1:2">
-      <c r="A312" s="3" t="s">
+      <c r="A312" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B312" s="3" t="s">
+      <c r="B312" s="1" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="1" spans="1:2">
-      <c r="A313" s="3" t="s">
+      <c r="A313" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B313" s="3" t="s">
+      <c r="B313" s="1" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="314" s="1" customFormat="1" spans="1:2">
-      <c r="A314" s="5" t="s">
+      <c r="A314" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B314" s="5" t="s">
+      <c r="B314" s="1" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="315" s="1" customFormat="1" spans="1:2">
-      <c r="A315" s="3" t="s">
+      <c r="A315" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B315" s="3" t="s">
+      <c r="B315" s="1" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="316" s="1" customFormat="1" spans="1:2">
-      <c r="A316" s="5" t="s">
+      <c r="A316" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B316" s="5" t="s">
+      <c r="B316" s="1" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="317" s="1" customFormat="1" spans="1:2">
-      <c r="A317" s="4" t="s">
+      <c r="A317" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B317" s="4" t="s">
+      <c r="B317" s="3" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="318" s="1" customFormat="1" spans="1:2">
-      <c r="A318" s="5" t="s">
+      <c r="A318" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B318" s="5" t="s">
+      <c r="B318" s="1" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="319" s="1" customFormat="1" spans="1:2">
-      <c r="A319" s="3" t="s">
+      <c r="A319" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B319" s="3" t="s">
+      <c r="B319" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="320" s="1" customFormat="1" spans="1:2">
-      <c r="A320" s="3" t="s">
+      <c r="A320" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B320" s="3" t="s">
+      <c r="B320" s="1" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="321" s="1" customFormat="1" spans="1:2">
-      <c r="A321" s="3" t="s">
+      <c r="A321" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B321" s="3" t="s">
+      <c r="B321" s="1" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="322" s="1" customFormat="1" spans="1:2">
-      <c r="A322" s="3" t="s">
+      <c r="A322" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B322" s="3" t="s">
+      <c r="B322" s="1" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="323" s="1" customFormat="1" spans="1:2">
-      <c r="A323" s="3" t="s">
+      <c r="A323" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="1" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="324" s="1" customFormat="1" spans="1:2">
-      <c r="A324" s="3" t="s">
+      <c r="A324" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B324" s="3" t="s">
+      <c r="B324" s="1" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="325" s="1" customFormat="1" spans="1:2">
-      <c r="A325" s="3" t="s">
+      <c r="A325" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B325" s="3" t="s">
+      <c r="B325" s="1" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" spans="1:2">
-      <c r="A326" s="5" t="s">
+      <c r="A326" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B326" s="5" t="s">
+      <c r="B326" s="1" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="327" s="1" customFormat="1" spans="1:2">
-      <c r="A327" s="5" t="s">
+      <c r="A327" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B327" s="5" t="s">
+      <c r="B327" s="1" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="328" s="1" customFormat="1" spans="1:2">
-      <c r="A328" s="5" t="s">
+      <c r="A328" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B328" s="5" t="s">
+      <c r="B328" s="1" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" spans="1:2">
-      <c r="A329" s="3" t="s">
+      <c r="A329" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B329" s="3" t="s">
+      <c r="B329" s="1" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="330" s="1" customFormat="1" spans="1:2">
-      <c r="A330" s="3" t="s">
+      <c r="A330" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B330" s="3" t="s">
+      <c r="B330" s="1" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="331" s="1" customFormat="1" spans="1:2">
-      <c r="A331" s="3" t="s">
+      <c r="A331" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B331" s="3" t="s">
+      <c r="B331" s="1" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" spans="1:2">
-      <c r="A332" s="3" t="s">
+      <c r="A332" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B332" s="3" t="s">
+      <c r="B332" s="1" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="333" s="1" customFormat="1" spans="1:2">
-      <c r="A333" s="3" t="s">
+      <c r="A333" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B333" s="3" t="s">
+      <c r="B333" s="1" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="334" s="1" customFormat="1" spans="1:2">
-      <c r="A334" s="3" t="s">
+      <c r="A334" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B334" s="3" t="s">
+      <c r="B334" s="1" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="335" s="1" customFormat="1" spans="1:2">
-      <c r="A335" s="3" t="s">
+      <c r="A335" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B335" s="3" t="s">
+      <c r="B335" s="1" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="336" s="1" customFormat="1" spans="1:2">
-      <c r="A336" s="3" t="s">
+      <c r="A336" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B336" s="3" t="s">
+      <c r="B336" s="1" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="337" s="1" customFormat="1" spans="1:2">
-      <c r="A337" s="3" t="s">
+      <c r="A337" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B337" s="3" t="s">
+      <c r="B337" s="1" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="338" s="1" customFormat="1" spans="1:2">
-      <c r="A338" s="3" t="s">
+      <c r="A338" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B338" s="3" t="s">
+      <c r="B338" s="1" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="339" s="1" customFormat="1" spans="1:2">
-      <c r="A339" s="3" t="s">
+      <c r="A339" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="B339" s="3" t="s">
+      <c r="B339" s="1" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="340" s="1" customFormat="1" spans="1:2">
-      <c r="A340" s="5" t="s">
+      <c r="A340" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B340" s="5" t="s">
+      <c r="B340" s="1" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" spans="1:2">
-      <c r="A341" s="3" t="s">
+      <c r="A341" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B341" s="3" t="s">
+      <c r="B341" s="1" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="342" s="1" customFormat="1" spans="1:2">
-      <c r="A342" s="3" t="s">
+      <c r="A342" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B342" s="3" t="s">
+      <c r="B342" s="1" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="343" s="1" customFormat="1" spans="1:2">
-      <c r="A343" s="3" t="s">
+      <c r="A343" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B343" s="3" t="s">
+      <c r="B343" s="1" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="344" s="1" customFormat="1" spans="1:2">
-      <c r="A344" s="3" t="s">
+      <c r="A344" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B344" s="3" t="s">
+      <c r="B344" s="1" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="1" spans="1:2">
-      <c r="A345" s="4" t="s">
+      <c r="A345" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B345" s="4" t="s">
+      <c r="B345" s="3" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="346" s="1" customFormat="1" spans="1:2">
-      <c r="A346" s="5" t="s">
+      <c r="A346" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B346" s="5" t="s">
+      <c r="B346" s="1" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="347" s="1" customFormat="1" spans="1:2">
-      <c r="A347" s="3" t="s">
+      <c r="A347" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B347" s="3" t="s">
+      <c r="B347" s="1" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="348" s="1" customFormat="1" spans="1:2">
-      <c r="A348" s="3" t="s">
+      <c r="A348" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B348" s="3" t="s">
+      <c r="B348" s="1" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="349" s="1" customFormat="1" spans="1:2">
-      <c r="A349" s="3" t="s">
+      <c r="A349" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B349" s="3" t="s">
+      <c r="B349" s="1" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="350" s="1" customFormat="1" spans="1:2">
-      <c r="A350" s="3" t="s">
+      <c r="A350" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B350" s="3" t="s">
+      <c r="B350" s="1" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" spans="1:2">
-      <c r="A351" s="3" t="s">
+      <c r="A351" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B351" s="3" t="s">
+      <c r="B351" s="1" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="352" s="1" customFormat="1" spans="1:2">
-      <c r="A352" s="4" t="s">
+      <c r="A352" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B352" s="4" t="s">
+      <c r="B352" s="3" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="353" s="1" customFormat="1" spans="1:2">
-      <c r="A353" s="3" t="s">
+      <c r="A353" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B353" s="3" t="s">
+      <c r="B353" s="1" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="354" s="1" customFormat="1" spans="1:2">
-      <c r="A354" s="3" t="s">
+      <c r="A354" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="B354" s="1" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="355" s="1" customFormat="1" spans="1:2">
-      <c r="A355" s="3" t="s">
+      <c r="A355" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B355" s="3" t="s">
+      <c r="B355" s="1" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="356" s="1" customFormat="1" spans="1:2">
-      <c r="A356" s="4" t="s">
+      <c r="A356" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B356" s="4" t="s">
+      <c r="B356" s="3" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="357" s="1" customFormat="1" spans="1:2">
-      <c r="A357" s="3" t="s">
+      <c r="A357" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="B357" s="3" t="s">
+      <c r="B357" s="1" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="3" t="s">
+      <c r="A358" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B358" s="3" t="s">
+      <c r="B358" s="1" t="s">
         <v>453</v>
       </c>
     </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B358" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:B358">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:B361" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:B361">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="B$1:B$1048576">
+  <conditionalFormatting sqref="B359">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B360">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B361">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B362">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B358 B363:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
